--- a/results/supp_data/Supplementary Data 4.xlsx
+++ b/results/supp_data/Supplementary Data 4.xlsx
@@ -1982,7 +1982,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stable identifier, matching Table S1.</t>
+          <t>Stable identifier, matching Supplementary Data 1.</t>
         </is>
       </c>
     </row>
